--- a/artfynd/A 20217-2026 artfynd.xlsx
+++ b/artfynd/A 20217-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AY12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,53 +675,52 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>133279702</v>
+        <v>133275893</v>
       </c>
       <c r="B2" t="n">
-        <v>58519</v>
+        <v>97435</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>102990</v>
+        <v>53</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Järnsparv</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Prunella modularis</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Fanders klippor, Fanders klippor, Ög</t>
+          <t>Nidingen, Ög</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>559562</v>
+        <v>559548</v>
       </c>
       <c r="R2" t="n">
-        <v>6414942</v>
+        <v>6414873</v>
       </c>
       <c r="S2" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -748,88 +747,75 @@
           <t>2026-05-09</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>11:06</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2026-05-09</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>11:06</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Linnea Druid</t>
+          <t>Emil Lindgren</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Linnea Druid</t>
+          <t>Emil Lindgren, Linnea Druid</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>133275787</v>
+        <v>133279748</v>
       </c>
       <c r="B3" t="n">
-        <v>98043</v>
+        <v>97435</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221945</v>
+        <v>53</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Nidingen, Ög</t>
+          <t>Sunnekärret, Sunnekärret, Ög</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>559538</v>
+        <v>559550</v>
       </c>
       <c r="R3" t="n">
-        <v>6414834</v>
+        <v>6414864</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -859,82 +845,87 @@
           <t>2026-05-09</t>
         </is>
       </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>11:10</t>
+        </is>
+      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2026-05-09</t>
         </is>
       </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>11:10</t>
+        </is>
+      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Emil Lindgren</t>
+          <t>Linnea Druid</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Emil Lindgren</t>
+          <t>Linnea Druid</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>133275893</v>
+        <v>133279857</v>
       </c>
       <c r="B4" t="n">
-        <v>97418</v>
+        <v>96783</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>53</v>
+        <v>2180</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Nidingen, Ög</t>
+          <t>Fanders klippor, Fanders klippor, Ög</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>559548</v>
+        <v>559545</v>
       </c>
       <c r="R4" t="n">
-        <v>6414873</v>
+        <v>6414897</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -961,69 +952,74 @@
           <t>2026-05-09</t>
         </is>
       </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>11:10</t>
+        </is>
+      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2026-05-09</t>
         </is>
       </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>11:10</t>
+        </is>
+      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Emil Lindgren</t>
+          <t>Linnea Druid</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Emil Lindgren, Linnea Druid</t>
+          <t>Linnea Druid</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>133275718</v>
+        <v>133275628</v>
       </c>
       <c r="B5" t="n">
-        <v>99178</v>
+        <v>96410</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>2812</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kransmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hylocomiadelphus triquetrus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ochyra &amp; Stebel</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
@@ -1034,10 +1030,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>559484</v>
+        <v>559391</v>
       </c>
       <c r="R5" t="n">
-        <v>6414827</v>
+        <v>6414845</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1097,42 +1093,42 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>133275700</v>
+        <v>133275759</v>
       </c>
       <c r="B6" t="n">
-        <v>99178</v>
+        <v>57972</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1140,10 +1136,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>559479</v>
+        <v>559534</v>
       </c>
       <c r="R6" t="n">
-        <v>6414828</v>
+        <v>6414832</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1184,7 +1180,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1203,10 +1198,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>133279857</v>
+        <v>133257699</v>
       </c>
       <c r="B7" t="n">
-        <v>96766</v>
+        <v>5181</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1214,37 +1209,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2180</v>
+        <v>100526</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Fanders klippor, Fanders klippor, Ög</t>
+          <t>Salbrohagen, Salbrohagen, Ög</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>559545</v>
+        <v>559400</v>
       </c>
       <c r="R7" t="n">
-        <v>6414897</v>
+        <v>6414848</v>
       </c>
       <c r="S7" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1273,7 +1268,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1283,7 +1278,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1298,22 +1293,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Linnea Druid</t>
+          <t>Malin Gröndahl Maass</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Linnea Druid</t>
+          <t>Malin Gröndahl Maass</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>133279748</v>
+        <v>133279702</v>
       </c>
       <c r="B8" t="n">
-        <v>97418</v>
+        <v>58519</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1321,37 +1316,42 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>53</v>
+        <v>102990</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Järnsparv</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Prunella modularis</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Sunnekärret, Sunnekärret, Ög</t>
+          <t>Fanders klippor, Fanders klippor, Ög</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>559550</v>
+        <v>559562</v>
       </c>
       <c r="R8" t="n">
-        <v>6414864</v>
+        <v>6414942</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1380,7 +1380,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1390,7 +1390,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1417,42 +1417,42 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>133275759</v>
+        <v>133275685</v>
       </c>
       <c r="B9" t="n">
-        <v>57972</v>
+        <v>99195</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1460,10 +1460,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>559534</v>
+        <v>559455</v>
       </c>
       <c r="R9" t="n">
-        <v>6414832</v>
+        <v>6414816</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1504,6 +1504,7 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1522,45 +1523,53 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>133257699</v>
+        <v>133275700</v>
       </c>
       <c r="B10" t="n">
-        <v>5181</v>
+        <v>99195</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Salbrohagen, Salbrohagen, Ög</t>
+          <t>Nidingen, Ög</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>559400</v>
+        <v>559479</v>
       </c>
       <c r="R10" t="n">
-        <v>6414848</v>
+        <v>6414828</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1590,49 +1599,40 @@
           <t>2026-05-09</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>11:54</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2026-05-09</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>11:54</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Malin Gröndahl Maass</t>
+          <t>Emil Lindgren</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Malin Gröndahl Maass</t>
+          <t>Emil Lindgren</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>133275685</v>
+        <v>133275718</v>
       </c>
       <c r="B11" t="n">
-        <v>99178</v>
+        <v>99195</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1659,7 +1659,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>60</t>
         </is>
       </c>
       <c r="J11" t="inlineStr"/>
@@ -1672,10 +1672,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>559455</v>
+        <v>559484</v>
       </c>
       <c r="R11" t="n">
-        <v>6414816</v>
+        <v>6414827</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1732,6 +1732,108 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>133275787</v>
+      </c>
+      <c r="B12" t="n">
+        <v>98060</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Nidingen, Ög</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>559538</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6414834</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Kinda</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Hycklinge</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="inlineStr"/>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Emil Lindgren</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Emil Lindgren</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 20217-2026 artfynd.xlsx
+++ b/artfynd/A 20217-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY12"/>
+  <dimension ref="A1:AZ12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -774,6 +779,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133275893</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -881,6 +891,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133279748</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -988,6 +1003,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133279857</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1090,6 +1110,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133275628</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1195,6 +1220,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133275759</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1302,6 +1332,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133257699</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1414,6 +1449,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133279702</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1520,6 +1560,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133275685</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1626,6 +1671,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133275700</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1732,6 +1782,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133275718</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1834,8 +1889,26 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133275787</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>